--- a/artfynd/A 7201-2025 artfynd.xlsx
+++ b/artfynd/A 7201-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>87896077</v>
+        <v>93551981</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56925</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,49 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>100045</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Målilla, Sm</t>
+          <t>Nydal, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551643.9664564751</v>
+        <v>551650</v>
       </c>
       <c r="R2" t="n">
-        <v>6360943.925149207</v>
+        <v>6361000</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +752,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-08-17</t>
+          <t>2021-05-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-08-17</t>
+          <t>2021-05-17</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ganska riklig</t>
+          <t>Flög söderut mot Norrlången</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,15 +787,117 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Gunnar Karlsson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Gunnar Karlsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>87896077</v>
+      </c>
+      <c r="B3" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Målilla, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>551644</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6360944</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Målilla</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2020-08-17</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2020-08-17</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ganska riklig</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Tony Svensson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Tony Svensson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7201-2025 artfynd.xlsx
+++ b/artfynd/A 7201-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -796,6 +801,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93551981</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,8 +908,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87896077</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>